--- a/data/Verzasca/investment_decision/Gerra_SFH_from_2015_investment_decision.xlsx
+++ b/data/Verzasca/investment_decision/Gerra_SFH_from_2015_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,24 +461,24 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_all_invested_available_unit</t>
@@ -490,7 +491,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -527,11 +528,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>2.329816963220044</v>
+        <v>0.2912271204025055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,30 +546,30 @@
         <v>1914.920754923092</v>
       </c>
       <c r="F3" t="n">
-        <v>2.329816963220052</v>
+        <v>0.2912271204025055</v>
       </c>
       <c r="G3" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="H3" t="n">
-        <v>2.329816963220044</v>
+        <v>0.2912271204025055</v>
       </c>
       <c r="I3" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="J3" t="n">
-        <v>2.329816963220052</v>
+        <v>0.2912271204025055</v>
       </c>
       <c r="K3" t="n">
         <v>1914.920754923092</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>10.31517150670982</v>
+        <v>13.40990116600141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,30 +583,30 @@
         <v>1914.920754923092</v>
       </c>
       <c r="F4" t="n">
-        <v>10.39724225714312</v>
+        <v>13.25637763324633</v>
       </c>
       <c r="G4" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="H4" t="n">
-        <v>10.31517150574165</v>
+        <v>13.33711451327821</v>
       </c>
       <c r="I4" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="J4" t="n">
-        <v>10.39724621630625</v>
+        <v>13.31523467249133</v>
       </c>
       <c r="K4" t="n">
         <v>1914.920754923092</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>10.31517150670982</v>
+        <v>13.40990116600141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,30 +620,30 @@
         <v>1914.920754923092</v>
       </c>
       <c r="F5" t="n">
-        <v>10.39724225714312</v>
+        <v>13.25637763324633</v>
       </c>
       <c r="G5" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="H5" t="n">
-        <v>10.31517150574165</v>
+        <v>13.33711451327821</v>
       </c>
       <c r="I5" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="J5" t="n">
-        <v>10.39724621630625</v>
+        <v>13.31523467249133</v>
       </c>
       <c r="K5" t="n">
         <v>1914.920754923092</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>10.44043858028306</v>
+        <v>13.40990116600141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,26 +657,26 @@
         <v>1914.920754923092</v>
       </c>
       <c r="F6" t="n">
-        <v>10.72676494951409</v>
+        <v>13.25637763324633</v>
       </c>
       <c r="G6" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="H6" t="n">
-        <v>10.73269800631753</v>
+        <v>13.33711451327821</v>
       </c>
       <c r="I6" t="n">
         <v>1914.920754923092</v>
       </c>
       <c r="J6" t="n">
-        <v>10.72676425489341</v>
+        <v>13.31523467249133</v>
       </c>
       <c r="K6" t="n">
         <v>1914.920754923092</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -683,36 +684,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -720,36 +721,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -757,36 +758,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -794,36 +795,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -831,40 +832,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Gerra_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Gerra_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.872381132384639</v>
+        <v>4.29035595505618</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000588077025882353</v>
+        <v>0.0004043029552941177</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,30 +879,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006272031600928257</v>
+        <v>0.0004043029552941177</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000588077025882353</v>
+        <v>0.0004043029552941177</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0006272031600928257</v>
+        <v>0.0004043029552941177</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0006983414682352942</v>
+        <v>0.0004916170100684414</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,30 +916,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006983414682352942</v>
+        <v>0.0004916170100684414</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0006983414682352942</v>
+        <v>0.0004916170100684414</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0007350962823529411</v>
+        <v>0.0004916170100684414</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0007718510964705883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0008453607247058824</v>
+        <v>0.0008009304877450805</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0008453607247058824</v>
+        <v>0.0007985413021088852</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0008453607247058824</v>
+        <v>0.0008086059105882317</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008453607247058824</v>
+        <v>0.0007718510964705883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,30 +990,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0008009304877450906</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0007985413021088852</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0008086059105882355</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0007718510964705883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,26 +1027,26 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0008009304877450906</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0008453607247058823</v>
+        <v>0.0007985413021088852</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0008453607247058824</v>
+        <v>0.0008086059105882355</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1082,7 +1083,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
@@ -1119,11 +1120,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.50767587</v>
+        <v>0.4295718900000001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F19" t="n">
-        <v>0.50767587</v>
+        <v>0.4358402233016784</v>
       </c>
       <c r="G19" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H19" t="n">
-        <v>0.50767587</v>
+        <v>0.4046990717453454</v>
       </c>
       <c r="I19" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J19" t="n">
-        <v>0.50767587</v>
+        <v>0.4044324639684592</v>
       </c>
       <c r="K19" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.50767587</v>
+        <v>0.4295718900000001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.50767587</v>
+        <v>0.4358402233016784</v>
       </c>
       <c r="G20" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H20" t="n">
-        <v>0.50767587</v>
+        <v>0.4046990717453454</v>
       </c>
       <c r="I20" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J20" t="n">
-        <v>0.50767587</v>
+        <v>0.4044324639684592</v>
       </c>
       <c r="K20" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.50767587</v>
+        <v>0.4295718900000001</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.50767587</v>
+        <v>0.4358402233016784</v>
       </c>
       <c r="G21" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H21" t="n">
-        <v>0.50767587</v>
+        <v>0.4046990717453454</v>
       </c>
       <c r="I21" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J21" t="n">
-        <v>0.50767587</v>
+        <v>0.4044324639684592</v>
       </c>
       <c r="K21" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,11 +1490,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.07810398</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,30 +1508,30 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.07183564669832168</v>
       </c>
       <c r="G29" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1029767982546547</v>
       </c>
       <c r="I29" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1032434060315409</v>
       </c>
       <c r="K29" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.07810398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,30 +1545,30 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.07183564669832168</v>
       </c>
       <c r="G30" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1029767982546547</v>
       </c>
       <c r="I30" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1032434060315409</v>
       </c>
       <c r="K30" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.07810398</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,26 +1582,26 @@
         <v>0.6560734320000002</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.07183564669832168</v>
       </c>
       <c r="G31" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.1029767982546547</v>
       </c>
       <c r="I31" t="n">
         <v>0.6560734320000002</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.103243406031541</v>
       </c>
       <c r="K31" t="n">
         <v>0.6560734320000002</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2118,7 +2119,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2192,7 +2193,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2266,7 +2267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2303,7 +2304,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2340,7 +2341,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2377,7 +2378,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
@@ -2414,11 +2415,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.8148445308824157</v>
+        <v>0.7938396065808588</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,30 +2433,30 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8058562059151194</v>
+        <v>0.7044877739153255</v>
       </c>
       <c r="G54" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7586312782476029</v>
+        <v>0.7912614683269894</v>
       </c>
       <c r="I54" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7525954122191539</v>
+        <v>0.70470589117841</v>
       </c>
       <c r="K54" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.8148445308824157</v>
+        <v>0.7938396065808588</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,30 +2470,30 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8058562059151194</v>
+        <v>0.7044877739153255</v>
       </c>
       <c r="G55" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7586312782476029</v>
+        <v>0.7912614683269893</v>
       </c>
       <c r="I55" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7525954122191539</v>
+        <v>0.70470589117841</v>
       </c>
       <c r="K55" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.8148445308824157</v>
+        <v>0.7938396065808588</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,26 +2507,26 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8058562059151194</v>
+        <v>0.7044877739153255</v>
       </c>
       <c r="G56" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7586312782476029</v>
+        <v>0.7912614683269893</v>
       </c>
       <c r="I56" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J56" t="n">
-        <v>0.7525954122191539</v>
+        <v>0.70470589117841</v>
       </c>
       <c r="K56" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2562,7 +2563,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2599,7 +2600,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2636,7 +2637,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2673,7 +2674,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2710,7 +2711,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2747,7 +2748,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
@@ -2784,11 +2785,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>1.009007942422957</v>
+        <v>0.4679761353565161</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,30 +2803,30 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F64" t="n">
-        <v>1.016185883189519</v>
+        <v>0.5590873788948511</v>
       </c>
       <c r="G64" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H64" t="n">
-        <v>1.065221195079127</v>
+        <v>0.4702681449744781</v>
       </c>
       <c r="I64" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J64" t="n">
-        <v>1.069446589551003</v>
+        <v>0.5565604706574535</v>
       </c>
       <c r="K64" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>1.009007942422957</v>
+        <v>0.4679761353565092</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,30 +2840,30 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F65" t="n">
-        <v>1.016185883189519</v>
+        <v>0.5590873788948511</v>
       </c>
       <c r="G65" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H65" t="n">
-        <v>1.065221195079127</v>
+        <v>0.4702681449744781</v>
       </c>
       <c r="I65" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J65" t="n">
-        <v>1.069446589551003</v>
+        <v>0.5565604706574535</v>
       </c>
       <c r="K65" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>1.25232413610029</v>
+        <v>0.4679761353565093</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,26 +2877,26 @@
         <v>3.876115529373662</v>
       </c>
       <c r="F66" t="n">
-        <v>1.254996438216901</v>
+        <v>0.5590873788948511</v>
       </c>
       <c r="G66" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="H66" t="n">
-        <v>1.302090489631401</v>
+        <v>0.4702681449744781</v>
       </c>
       <c r="I66" t="n">
         <v>3.876115529373662</v>
       </c>
       <c r="J66" t="n">
-        <v>1.308257247235382</v>
+        <v>0.5565604706574535</v>
       </c>
       <c r="K66" t="n">
         <v>3.876115529373662</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2932,7 +2933,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2969,7 +2970,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3006,7 +3007,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3080,7 +3081,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3117,7 +3118,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3154,7 +3155,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3191,7 +3192,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3228,7 +3229,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3265,7 +3266,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3302,7 +3303,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
@@ -3339,7 +3340,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
@@ -3376,7 +3377,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3413,7 +3414,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
